--- a/Result/profitability/6120.xlsx
+++ b/Result/profitability/6120.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.05875000000000001</v>
+        <v>0.13625</v>
       </c>
       <c r="N2" t="n">
-        <v>4.74625</v>
+        <v>4.49375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.09250000000000001</v>
+        <v>0.05625000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>4.162500000000001</v>
+        <v>3.845</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,19 +899,19 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.14</v>
+        <v>0.06125000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>3.125</v>
+        <v>3.09875</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.395</v>
+        <v>-0.18625</v>
       </c>
       <c r="N5" t="n">
-        <v>2.455</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.39875</v>
+        <v>-0.195</v>
       </c>
       <c r="N6" t="n">
-        <v>2.07875</v>
+        <v>1.90125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3337499999999999</v>
+        <v>-0.135</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>2.48375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.225</v>
+        <v>-0.00874999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>3.28875</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01250000000000002</v>
+        <v>0.01250000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>4.8725</v>
@@ -2026,7 +2026,7 @@
         <v>0.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5437500000000001</v>
+        <v>0.54375</v>
       </c>
       <c r="N13" t="n">
         <v>8.657500000000001</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6120</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4230</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4058</v>
+      </c>
+      <c r="E75" t="n">
+        <v>172</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-211</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1179</v>
+      </c>
+      <c r="J75" t="n">
+        <v>968</v>
+      </c>
+      <c r="K75" t="n">
+        <v>945</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.07375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-11.53333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4899999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1372549019607843</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-18.55555555555556</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.8400000000000007</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1714285714285716</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
